--- a/docs/graph-editor/LabelEditor_仕様一覧.xlsx
+++ b/docs/graph-editor/LabelEditor_仕様一覧.xlsx
@@ -629,7 +629,7 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>graph2 出力 SVG を読み込む</t>
+          <t>pie-chart 出力 SVG を読み込む</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>graph2 出力 SVG</t>
+          <t>pie-chart 出力 SVG</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>UMD（graph2 と共有）</t>
+          <t>UMD（pie-chart と共有）</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
